--- a/Italian Serie A/Y.xlsx
+++ b/Italian Serie A/Y.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3292"/>
+  <dimension ref="A1:C3301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36646,6 +36646,105 @@
         <v>0.1014091250758634</v>
       </c>
     </row>
+    <row r="3293">
+      <c r="A3293" t="n">
+        <v>0.4374868101876332</v>
+      </c>
+      <c r="B3293" t="n">
+        <v>0.293796697863784</v>
+      </c>
+      <c r="C3293" t="n">
+        <v>0.2687164919485829</v>
+      </c>
+    </row>
+    <row r="3294">
+      <c r="A3294" t="n">
+        <v>0.3462878992961559</v>
+      </c>
+      <c r="B3294" t="n">
+        <v>0.3131361667569031</v>
+      </c>
+      <c r="C3294" t="n">
+        <v>0.340575933946941</v>
+      </c>
+    </row>
+    <row r="3295">
+      <c r="A3295" t="n">
+        <v>0.2748433569972168</v>
+      </c>
+      <c r="B3295" t="n">
+        <v>0.3027935288952389</v>
+      </c>
+      <c r="C3295" t="n">
+        <v>0.4223631141075442</v>
+      </c>
+    </row>
+    <row r="3296">
+      <c r="A3296" t="n">
+        <v>0.6254513523966371</v>
+      </c>
+      <c r="B3296" t="n">
+        <v>0.2330026517026908</v>
+      </c>
+      <c r="C3296" t="n">
+        <v>0.141545995900672</v>
+      </c>
+    </row>
+    <row r="3297">
+      <c r="A3297" t="n">
+        <v>0.6760709663049426</v>
+      </c>
+      <c r="B3297" t="n">
+        <v>0.2054498706313931</v>
+      </c>
+      <c r="C3297" t="n">
+        <v>0.1184791630636644</v>
+      </c>
+    </row>
+    <row r="3298">
+      <c r="A3298" t="n">
+        <v>0.268190411788307</v>
+      </c>
+      <c r="B3298" t="n">
+        <v>0.2698323939012967</v>
+      </c>
+      <c r="C3298" t="n">
+        <v>0.4619771943103961</v>
+      </c>
+    </row>
+    <row r="3299">
+      <c r="A3299" t="n">
+        <v>0.4952931031255983</v>
+      </c>
+      <c r="B3299" t="n">
+        <v>0.2705843059288617</v>
+      </c>
+      <c r="C3299" t="n">
+        <v>0.2341225909455399</v>
+      </c>
+    </row>
+    <row r="3300">
+      <c r="A3300" t="n">
+        <v>0.4040942580191476</v>
+      </c>
+      <c r="B3300" t="n">
+        <v>0.3007726142490107</v>
+      </c>
+      <c r="C3300" t="n">
+        <v>0.2951331277318417</v>
+      </c>
+    </row>
+    <row r="3301">
+      <c r="A3301" t="n">
+        <v>0.575362818260393</v>
+      </c>
+      <c r="B3301" t="n">
+        <v>0.2564092714259082</v>
+      </c>
+      <c r="C3301" t="n">
+        <v>0.1682279103136987</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
